--- a/Roboz Hunor/erettsegi/szerencsepentek.xlsx
+++ b/Roboz Hunor/erettsegi/szerencsepentek.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hunor\Desktop\Hunor\Info\info_fakt_git\fakt2025\Roboz Hunor\erettsegi\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Roboz Hunor\git\fakt2025\Roboz Hunor\erettsegi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ED41D54-A26C-4BFC-B065-5E4DD021A68A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8934EF8-88C4-4412-B4E6-38A7D49DDAA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{8DC387A2-28B4-42ED-B75A-61FCADD68F93}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" activeTab="1" xr2:uid="{8DC387A2-28B4-42ED-B75A-61FCADD68F93}"/>
   </bookViews>
   <sheets>
     <sheet name="Diagram1" sheetId="2" r:id="rId1"/>
@@ -28,8 +28,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -116,9 +114,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="General&quot; pont&quot;"/>
+    <numFmt numFmtId="164" formatCode="General&quot; pont&quot;"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -203,7 +201,16 @@
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -212,15 +219,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -389,19 +387,19 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>2</c:v>
@@ -410,13 +408,13 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>2</c:v>
@@ -1501,95 +1499,95 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26944F2D-413E-4B8C-BA40-162E03EE6CF3}">
   <dimension ref="A1:K32"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.77734375" customWidth="1"/>
+    <col min="1" max="1" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.75" customWidth="1"/>
     <col min="3" max="3" width="7" customWidth="1"/>
-    <col min="4" max="4" width="6.88671875" customWidth="1"/>
+    <col min="4" max="4" width="6.875" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="8.6640625" customWidth="1"/>
+    <col min="6" max="6" width="8.625" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="9" max="9" width="8.33203125" customWidth="1"/>
-    <col min="10" max="10" width="10.33203125" customWidth="1"/>
-    <col min="11" max="11" width="16.5546875" customWidth="1"/>
+    <col min="9" max="9" width="8.375" customWidth="1"/>
+    <col min="10" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="11" width="16.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="7">
+    <row r="1" spans="1:11">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4">
         <v>1000</v>
       </c>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="6" t="str">
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="str">
         <f ca="1">IF(RANDBETWEEN(0,1)=0,"f","i")</f>
+        <v>f</v>
+      </c>
+      <c r="C2" s="3" t="str">
+        <f t="shared" ref="C2:E2" ca="1" si="0">IF(RANDBETWEEN(0,1)=0,"f","i")</f>
         <v>i</v>
       </c>
-      <c r="C2" s="6" t="str">
-        <f t="shared" ref="C2:E2" ca="1" si="0">IF(RANDBETWEEN(0,1)=0,"f","i")</f>
+      <c r="D2" s="3" t="str">
+        <f t="shared" ca="1" si="0"/>
         <v>f</v>
       </c>
-      <c r="D2" s="6" t="str">
+      <c r="E2" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>i</v>
       </c>
-      <c r="E2" s="6" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>f</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="8" t="s">
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="J4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="K4" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="8" t="s">
+      <c r="B5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="5">
         <f ca="1">SUM(B20:E20)</f>
         <v>2</v>
       </c>
@@ -1597,35 +1595,35 @@
         <f ca="1">F5*$B$1</f>
         <v>2000</v>
       </c>
-      <c r="I5" s="8">
-        <v>0</v>
-      </c>
-      <c r="J5" s="8">
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
         <f ca="1">COUNTIFS(F5:F17,I5)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5" s="2">
         <f ca="1">IF(J5&gt;0,$B$1*I5*J5," ")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="8">
+      <c r="D6" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="5">
         <f t="shared" ref="F6:F17" ca="1" si="1">SUM(B21:E21)</f>
         <v>2</v>
       </c>
@@ -1633,46 +1631,46 @@
         <f t="shared" ref="G6:G17" ca="1" si="2">F6*$B$1</f>
         <v>2000</v>
       </c>
-      <c r="I6" s="8">
-        <v>1</v>
-      </c>
-      <c r="J6" s="8">
+      <c r="I6" s="5">
+        <v>1</v>
+      </c>
+      <c r="J6" s="5">
         <f t="shared" ref="J6:J9" ca="1" si="3">COUNTIFS(F6:F18,I6)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6" s="2">
         <f t="shared" ref="K6:K9" ca="1" si="4">IF(J6&gt;0,$B$1*I6*J6," ")</f>
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="8" t="s">
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="8" t="s">
+      <c r="D7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G7" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>4000</v>
-      </c>
-      <c r="I7" s="8">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
         <v>2</v>
       </c>
-      <c r="J7" s="8">
+      <c r="J7" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>5</v>
       </c>
@@ -1681,23 +1679,23 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="8" t="s">
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="8">
+      <c r="E8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="5">
         <f t="shared" ca="1" si="1"/>
         <v>2</v>
       </c>
@@ -1705,121 +1703,121 @@
         <f t="shared" ca="1" si="2"/>
         <v>2000</v>
       </c>
-      <c r="I8" s="8">
+      <c r="I8" s="5">
         <v>3</v>
       </c>
-      <c r="J8" s="8">
+      <c r="J8" s="5">
+        <f t="shared" ca="1" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="K8" s="2">
+        <f t="shared" ca="1" si="4"/>
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="5">
+        <f t="shared" ca="1" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="G9" s="2">
+        <f t="shared" ca="1" si="2"/>
+        <v>4000</v>
+      </c>
+      <c r="I9" s="5">
+        <v>4</v>
+      </c>
+      <c r="J9" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>2</v>
       </c>
-      <c r="K8" s="2">
+      <c r="K9" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" s="8">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G9" s="2">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I9" s="8">
-        <v>4</v>
-      </c>
-      <c r="J9" s="8">
-        <f t="shared" ca="1" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K9" s="1" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="8" t="s">
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="8">
+      <c r="D10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="5">
+        <f t="shared" ca="1" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="G10" s="2">
+        <f t="shared" ca="1" si="2"/>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="5">
         <f t="shared" ca="1" si="1"/>
         <v>3</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G11" s="2">
         <f t="shared" ca="1" si="2"/>
         <v>3000</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="8">
-        <f t="shared" ca="1" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="G11" s="2">
-        <f t="shared" ca="1" si="2"/>
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11">
       <c r="A12" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="8">
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="5">
         <f t="shared" ca="1" si="1"/>
         <v>2</v>
       </c>
@@ -1828,23 +1826,23 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11">
       <c r="A13" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D13" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" s="8">
+      <c r="D13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" s="5">
         <f t="shared" ca="1" si="1"/>
         <v>2</v>
       </c>
@@ -1853,48 +1851,48 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11">
       <c r="A14" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="8" t="s">
+      <c r="C14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" s="8">
+      <c r="E14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G14" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" s="8">
+      <c r="D15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" s="5">
         <f t="shared" ca="1" si="1"/>
         <v>2</v>
       </c>
@@ -1903,48 +1901,48 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11">
       <c r="A16" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="8" t="s">
+      <c r="B16" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D16" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" s="8">
+      <c r="D16" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G16" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="E17" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F17" s="8">
+      <c r="F17" s="5">
         <f t="shared" ca="1" si="1"/>
         <v>2</v>
       </c>
@@ -1953,277 +1951,277 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" hidden="1">
       <c r="A20" t="s">
         <v>8</v>
       </c>
       <c r="B20">
         <f ca="1">IF(B5=B$2,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20">
         <f t="shared" ref="C20:E20" ca="1" si="5">IF(C5=C$2,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20">
         <f t="shared" ca="1" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20">
         <f t="shared" ca="1" si="5"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" hidden="1">
       <c r="A21" t="s">
         <v>11</v>
       </c>
       <c r="B21">
         <f t="shared" ref="B21:E32" ca="1" si="6">IF(B6=B$2,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C21">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" hidden="1">
       <c r="A22" t="s">
         <v>12</v>
       </c>
       <c r="B22">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C22">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" hidden="1">
       <c r="A23" t="s">
         <v>13</v>
       </c>
       <c r="B23">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C23">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" hidden="1">
       <c r="A24" t="s">
         <v>14</v>
       </c>
       <c r="B24">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C24">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" hidden="1">
       <c r="A25" t="s">
         <v>15</v>
       </c>
       <c r="B25">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C25">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" hidden="1">
       <c r="A26" t="s">
         <v>16</v>
       </c>
       <c r="B26">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C26">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" hidden="1">
       <c r="A27" t="s">
         <v>17</v>
       </c>
       <c r="B27">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C27">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" hidden="1">
       <c r="A28" t="s">
         <v>18</v>
       </c>
       <c r="B28">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C28">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" hidden="1">
       <c r="A29" t="s">
         <v>19</v>
       </c>
       <c r="B29">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C29">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D29">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" hidden="1">
       <c r="A30" t="s">
         <v>20</v>
       </c>
       <c r="B30">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C30">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" hidden="1">
       <c r="A31" t="s">
         <v>21</v>
       </c>
       <c r="B31">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C31">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" hidden="1">
       <c r="A32" t="s">
         <v>22</v>
       </c>
       <c r="B32">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C32">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
